--- a/트리.xlsx
+++ b/트리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\merge-rpg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62EC0EC7-AFA2-4567-8273-DE91D1449D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA1B35F-FC09-4D9C-B2F0-40222CD07831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7530" yWindow="1110" windowWidth="21150" windowHeight="14505" xr2:uid="{4F9E2AE5-4C94-4635-AAAB-E8B73292F854}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F9E2AE5-4C94-4635-AAAB-E8B73292F854}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="247">
   <si>
     <t>선술집</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,21 +92,10 @@
     <t>생성 블록</t>
   </si>
   <si>
-    <t>기사단 훈련소</t>
-  </si>
-  <si>
-    <t>기사단 훈련소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사냥꾼 야영지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마도 학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>성당</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -143,26 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>숏보우 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우드스테프 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나이프 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>숏소드 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>라이더</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,15 +144,844 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>롱소드 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스피어 lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성경 lv.3</t>
+    <t>신병 훈련소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트라이이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위자드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소서러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팔머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴디트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사격 훈련장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추적자 양성소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비술 연구소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성직자 수련원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순례자 회랑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은신처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도적 소굴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원소 연구소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디펜더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐벌리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헌터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레인저</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>트래퍼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스카우트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>룬캐스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>워록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서머너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비숍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채플린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몽크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>템플 가드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어쌔신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스토커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 나이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로열 가드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이 캐벌리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로열 랜서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호크아이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윈드러너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비스트 스토커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아크메이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타시어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>둠브링어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세인트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엑소시스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디사이플</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저스티카르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬텀 블레이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트 프라우러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블레이드 댄서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크루세이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>템플러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>템페스트 랜서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데드아이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패스파인더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섀도우 체이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로노맨서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디아볼리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아케온</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오라클</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인퀴지터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>애스킷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세이크리드 가드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 리퍼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섀도우 워커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이언 피스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀리 바인더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클레이모어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이트 브링거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브로드 소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파르티잔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스톰 슬레이어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재벌린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>트라이던트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>트리톤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매직 스태프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실반 보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이글 크로스 보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글라디우스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 버스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워실드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임페리얼 실드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈페리얼 슈터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쯔바이 보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 듀얼소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그레이트 보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로스 보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 실드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스톡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스파다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베놈 마스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글러브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 할버드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 대거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 크로우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이피어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글레디에이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버서커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 키퍼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세인트 캐벌리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매직 듀얼 소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인피니티 소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핸드 엑스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이랜드 엑스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세비노스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리머스 스태프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글레시어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리멘탈 마스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 완드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아케인 셰이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리버스 완드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사제의 십자가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모닝 스타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛의 십자가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성자의 십자가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>워 피크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 할버드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블래스 크래셔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은의 마도서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사술의 마도서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>심연의 마도서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리즘 수정구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛의 수정구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진리의 수정구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블랙 크로우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초기 제공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롱소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스피어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롱보우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>듀얼소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초급 법전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묵주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초기 스페이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 스페이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 스페이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 스페이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4차 스페이서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기사단 막사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕립 기사단 본부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성전 기사단 성소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패병 수련장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근위대 성채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>템플 기사단 요새</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기병대 마구간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황실 기병대 본영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성마 기병단 성소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창기병 연무장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕립 창기병단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭풍 창기병단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사냥꾼 산장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매의 전망대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵의 사격장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲 감시 초소</t>
+  </si>
+  <si>
+    <t>함정 공방</t>
+  </si>
+  <si>
+    <t>야수 추적 캠프</t>
+  </si>
+  <si>
+    <t>그림자 추적소</t>
+  </si>
+  <si>
+    <t>정찰대 초소</t>
+  </si>
+  <si>
+    <t>검무단 무대</t>
+  </si>
+  <si>
+    <t>결투 검술관</t>
+  </si>
+  <si>
+    <t>원소 제단</t>
+  </si>
+  <si>
+    <t>대마법사의 탑</t>
+  </si>
+  <si>
+    <t>원소 대성소</t>
+  </si>
+  <si>
+    <t>룬 각인소</t>
+  </si>
+  <si>
+    <t>별빛 관측소</t>
+  </si>
+  <si>
+    <t>시간의 회랑</t>
+  </si>
+  <si>
+    <t>흑마법 연구실</t>
+  </si>
+  <si>
+    <t>파멸의 제단</t>
+  </si>
+  <si>
+    <t>심연의 성소</t>
+  </si>
+  <si>
+    <t>소환 의식장</t>
+  </si>
+  <si>
+    <t>환령 계약소</t>
+  </si>
+  <si>
+    <t>고대 지식의 아카이브</t>
+  </si>
+  <si>
+    <t>주교관</t>
+  </si>
+  <si>
+    <t>성인의 성소</t>
+  </si>
+  <si>
+    <t>신탁의 성역</t>
+  </si>
+  <si>
+    <t>예배 전당</t>
+  </si>
+  <si>
+    <t>구마 의식소</t>
+  </si>
+  <si>
+    <t>이단 심문소</t>
+  </si>
+  <si>
+    <t>수도원 수련장</t>
+  </si>
+  <si>
+    <t>고행자의 도장</t>
+  </si>
+  <si>
+    <t>금욕자의 암자</t>
+  </si>
+  <si>
+    <t>성전 경비대</t>
+  </si>
+  <si>
+    <t>심판의 법정</t>
+  </si>
+  <si>
+    <t>성역 수비대</t>
+  </si>
+  <si>
+    <t>암살자 은거지</t>
+  </si>
+  <si>
+    <t>유령검 무기고</t>
+  </si>
+  <si>
+    <t>혈월 처형장</t>
+  </si>
+  <si>
+    <t>잠복자의 골목</t>
+  </si>
+  <si>
+    <t>야행자의 뒷골목</t>
+  </si>
+  <si>
+    <t>그림자 회랑</t>
+  </si>
+  <si>
+    <t>검투장</t>
+  </si>
+  <si>
+    <t>광전사의 투기장</t>
+  </si>
+  <si>
+    <t>피의 수호소</t>
+  </si>
+  <si>
+    <t>독약 공방</t>
+  </si>
+  <si>
+    <t>맹독 연구소</t>
+  </si>
+  <si>
+    <t>역병 정화소</t>
+  </si>
+  <si>
+    <t>개척자의 길목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바람길 전초기지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베놈리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우드 스테프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리멘탈리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이그 베인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서몬마스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이퍼 블로우건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 블로우건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이그 스팅어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>니들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바실리스크 팽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -208,20 +1006,116 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -230,18 +1124,69 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -249,6 +1194,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -577,203 +1527,1441 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63BAE74-44C1-40DE-B8C0-D2A46F4CAF81}">
-  <dimension ref="B1:J17"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="4" max="4" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
-    <col min="8" max="8" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" customWidth="1"/>
+    <col min="12" max="12" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.125" customWidth="1"/>
+    <col min="16" max="16" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.875" customWidth="1"/>
+    <col min="19" max="19" width="19.625" customWidth="1"/>
+    <col min="20" max="20" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.25" customWidth="1"/>
+    <col min="22" max="22" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="13"/>
+      <c r="V2" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="V3" s="15"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="M6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="L9" s="9"/>
+      <c r="M9" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="T9" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="L11" s="9"/>
+      <c r="M11" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="K14" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="S14" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="T14" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="T15" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="O17" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="S17" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="T17" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="K18" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="T18" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O19" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S19" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="T19" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="S20" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="T20" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="S21" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="T21" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
+      <c r="K22" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+    </row>
+    <row r="33" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+    </row>
+    <row r="34" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+    </row>
+    <row r="35" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+    </row>
+    <row r="36" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+    </row>
+    <row r="37" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+    </row>
+    <row r="38" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+    </row>
+    <row r="39" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+    </row>
+    <row r="40" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+    </row>
+    <row r="41" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+    </row>
+    <row r="42" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+    </row>
+    <row r="43" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+    </row>
+    <row r="44" spans="10:16" x14ac:dyDescent="0.3">
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C2:D2"/>
+  <mergeCells count="71">
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="G12:G13"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H20:H23"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="L22:L23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
